--- a/Tạp hóa/Kế hoạch kinh doanh/Kế hoạch kinh doanh.xlsx
+++ b/Tạp hóa/Kế hoạch kinh doanh/Kế hoạch kinh doanh.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LeVeL infinity\Desktop\Tạp hóa\Kế hoạch kinh doanh\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LeVeL infinity\Desktop\BackUp\backup-PC\Tạp hóa\Kế hoạch kinh doanh\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A7E9A4A-929E-41FC-9DAE-1C1955247D61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EA8AE97-5B76-415C-B56B-F1701F9C1D61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="2" xr2:uid="{AC7C96C8-729D-4A1A-A481-EBFA6B52E612}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="3" xr2:uid="{AC7C96C8-729D-4A1A-A481-EBFA6B52E612}"/>
   </bookViews>
   <sheets>
     <sheet name="Mẫu" sheetId="1" r:id="rId1"/>
@@ -656,7 +656,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -746,6 +746,19 @@
     <xf numFmtId="0" fontId="7" fillId="9" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="12" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -764,17 +777,14 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -788,30 +798,17 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="8" fillId="6" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="12" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="11" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1160,44 +1157,44 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71173555-DE94-44BF-8C2F-B3637FE4CFBB}">
   <dimension ref="A1:J32"/>
-  <sheetFormatPr defaultColWidth="9.09765625" defaultRowHeight="30.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="30.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.8984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.8984375" style="1" customWidth="1"/>
-    <col min="5" max="6" width="9.8984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.8984375" style="1" customWidth="1"/>
-    <col min="8" max="9" width="9.8984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.8984375" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.09765625" style="1"/>
+    <col min="3" max="3" width="9.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.875" style="1" customWidth="1"/>
+    <col min="5" max="6" width="9.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.875" style="1" customWidth="1"/>
+    <col min="8" max="9" width="9.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.875" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="9.125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="34" t="s">
+      <c r="A1" s="42" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="31" t="s">
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="32"/>
-      <c r="H1" s="33"/>
-      <c r="I1" s="31" t="s">
+      <c r="G1" s="39"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="J1" s="32"/>
+      <c r="J1" s="39"/>
     </row>
     <row r="2" spans="1:10" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="36"/>
-      <c r="B2" s="36"/>
+      <c r="A2" s="43"/>
+      <c r="B2" s="43"/>
       <c r="C2" s="2" t="s">
         <v>4</v>
       </c>
@@ -1718,72 +1715,72 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72D4AFF4-CBFB-4BD9-B291-CDCA5DA3AC91}">
   <dimension ref="A1:AC34"/>
-  <sheetFormatPr defaultColWidth="9.09765625" defaultRowHeight="30.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="30.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="8" width="14.09765625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="9.8984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.8984375" style="1" customWidth="1"/>
-    <col min="11" max="12" width="9.09765625" style="1"/>
-    <col min="13" max="13" width="53.59765625" style="1" customWidth="1"/>
-    <col min="14" max="14" width="9.09765625" style="1"/>
+    <col min="3" max="8" width="14.125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="9.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.875" style="1" customWidth="1"/>
+    <col min="11" max="12" width="9.125" style="1"/>
+    <col min="13" max="13" width="53.625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="9.125" style="1"/>
     <col min="15" max="15" width="53" style="1" customWidth="1"/>
-    <col min="16" max="16" width="9.09765625" style="1"/>
-    <col min="17" max="24" width="16.09765625" style="1" customWidth="1"/>
-    <col min="25" max="25" width="21.796875" style="1" customWidth="1"/>
-    <col min="26" max="28" width="16.09765625" style="1" customWidth="1"/>
+    <col min="16" max="16" width="9.125" style="1"/>
+    <col min="17" max="24" width="16.125" style="1" customWidth="1"/>
+    <col min="25" max="25" width="21.75" style="1" customWidth="1"/>
+    <col min="26" max="28" width="16.125" style="1" customWidth="1"/>
     <col min="29" max="29" width="23.5" style="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.09765625" style="1"/>
+    <col min="30" max="16384" width="9.125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="41" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="43" t="s">
+      <c r="A1" s="47" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43" t="s">
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="43"/>
-      <c r="H1" s="43"/>
-      <c r="I1" s="37" t="s">
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="J1" s="38"/>
-      <c r="M1" s="45" t="s">
+      <c r="J1" s="52"/>
+      <c r="M1" s="31" t="s">
         <v>15</v>
       </c>
       <c r="N1" s="26"/>
-      <c r="O1" s="45" t="s">
+      <c r="O1" s="31" t="s">
         <v>28</v>
       </c>
       <c r="P1" s="26"/>
-      <c r="Q1" s="48" t="s">
+      <c r="Q1" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="R1" s="48"/>
-      <c r="S1" s="48"/>
-      <c r="T1" s="48"/>
-      <c r="U1" s="48"/>
-      <c r="V1" s="48"/>
-      <c r="W1" s="48"/>
-      <c r="X1" s="48"/>
-      <c r="Y1" s="48"/>
-      <c r="Z1" s="48"/>
-      <c r="AA1" s="48"/>
-      <c r="AB1" s="48"/>
+      <c r="R1" s="45"/>
+      <c r="S1" s="45"/>
+      <c r="T1" s="45"/>
+      <c r="U1" s="45"/>
+      <c r="V1" s="45"/>
+      <c r="W1" s="45"/>
+      <c r="X1" s="45"/>
+      <c r="Y1" s="45"/>
+      <c r="Z1" s="45"/>
+      <c r="AA1" s="45"/>
+      <c r="AB1" s="45"/>
     </row>
     <row r="2" spans="1:29" ht="30.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="42"/>
-      <c r="B2" s="44"/>
+      <c r="A2" s="48"/>
+      <c r="B2" s="50"/>
       <c r="C2" s="8" t="s">
         <v>4</v>
       </c>
@@ -1814,33 +1811,33 @@
       <c r="O2" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="Q2" s="49" t="s">
+      <c r="Q2" s="44" t="s">
         <v>39</v>
       </c>
-      <c r="R2" s="49" t="s">
+      <c r="R2" s="44" t="s">
         <v>49</v>
       </c>
-      <c r="S2" s="49" t="s">
+      <c r="S2" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="T2" s="53" t="s">
+      <c r="T2" s="46" t="s">
         <v>40</v>
       </c>
-      <c r="U2" s="53"/>
-      <c r="V2" s="49" t="s">
+      <c r="U2" s="46"/>
+      <c r="V2" s="44" t="s">
         <v>42</v>
       </c>
-      <c r="W2" s="49"/>
-      <c r="X2" s="49"/>
-      <c r="Y2" s="54" t="s">
+      <c r="W2" s="44"/>
+      <c r="X2" s="44"/>
+      <c r="Y2" s="37" t="s">
         <v>46</v>
       </c>
-      <c r="Z2" s="49" t="s">
+      <c r="Z2" s="44" t="s">
         <v>51</v>
       </c>
-      <c r="AA2" s="49"/>
-      <c r="AB2" s="49"/>
-      <c r="AC2" s="54" t="s">
+      <c r="AA2" s="44"/>
+      <c r="AB2" s="44"/>
+      <c r="AC2" s="37" t="s">
         <v>55</v>
       </c>
     </row>
@@ -1877,13 +1874,13 @@
       <c r="O3" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="Q3" s="49"/>
-      <c r="R3" s="49"/>
-      <c r="S3" s="49"/>
-      <c r="T3" s="55" t="s">
+      <c r="Q3" s="44"/>
+      <c r="R3" s="44"/>
+      <c r="S3" s="44"/>
+      <c r="T3" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="U3" s="55" t="s">
+      <c r="U3" s="36" t="s">
         <v>41</v>
       </c>
       <c r="V3" s="8" t="s">
@@ -1895,7 +1892,7 @@
       <c r="X3" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="Y3" s="54" t="s">
+      <c r="Y3" s="37" t="s">
         <v>47</v>
       </c>
       <c r="Z3" s="8" t="s">
@@ -1907,11 +1904,11 @@
       <c r="AB3" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="AC3" s="54" t="s">
+      <c r="AC3" s="37" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="30.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:29" ht="30.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="11">
         <v>45749</v>
       </c>
@@ -1944,51 +1941,51 @@
       <c r="O4" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="Q4" s="47" t="s">
+      <c r="Q4" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="R4" s="50">
+      <c r="R4" s="33">
         <f>F34</f>
         <v>2685553</v>
       </c>
-      <c r="S4" s="50">
+      <c r="S4" s="33">
         <f>R4*0.86</f>
         <v>2309575.58</v>
       </c>
-      <c r="T4" s="51">
+      <c r="T4" s="34">
         <v>192550</v>
       </c>
-      <c r="U4" s="51">
+      <c r="U4" s="34">
         <v>1100000</v>
       </c>
-      <c r="V4" s="50">
+      <c r="V4" s="33">
         <v>70000</v>
       </c>
-      <c r="W4" s="50">
+      <c r="W4" s="33">
         <v>2000</v>
       </c>
-      <c r="X4" s="50">
+      <c r="X4" s="33">
         <v>30000</v>
       </c>
-      <c r="Y4" s="52">
+      <c r="Y4" s="35">
         <f>R4-S4-T4-U4-V4-W4-X4</f>
         <v>-1018572.5800000001</v>
       </c>
-      <c r="Z4" s="50">
+      <c r="Z4" s="33">
         <v>20000</v>
       </c>
-      <c r="AA4" s="50">
+      <c r="AA4" s="33">
         <v>10000</v>
       </c>
-      <c r="AB4" s="50">
+      <c r="AB4" s="33">
         <v>10000</v>
       </c>
-      <c r="AC4" s="52">
+      <c r="AC4" s="35">
         <f>Y4-Z4-AA4-AB4</f>
         <v>-1058572.58</v>
       </c>
     </row>
-    <row r="5" spans="1:29" ht="30.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:29" ht="30.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="11">
         <v>45750</v>
       </c>
@@ -2021,46 +2018,46 @@
       <c r="O5" s="29" t="s">
         <v>32</v>
       </c>
-      <c r="Q5" s="47" t="s">
+      <c r="Q5" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="R5" s="50">
+      <c r="R5" s="33">
         <f>G34</f>
         <v>1416890</v>
       </c>
-      <c r="S5" s="50">
+      <c r="S5" s="33">
         <f>R5*0.86</f>
         <v>1218525.3999999999</v>
       </c>
-      <c r="T5" s="51">
+      <c r="T5" s="34">
         <v>60330</v>
       </c>
-      <c r="U5" s="51">
+      <c r="U5" s="34">
         <v>350000</v>
       </c>
-      <c r="V5" s="50">
+      <c r="V5" s="33">
         <v>10000</v>
       </c>
-      <c r="W5" s="50">
+      <c r="W5" s="33">
         <v>2000</v>
       </c>
-      <c r="X5" s="50">
+      <c r="X5" s="33">
         <v>10000</v>
       </c>
-      <c r="Y5" s="52">
+      <c r="Y5" s="35">
         <f>R5-S5-T5-U5-V5-W5-X5</f>
         <v>-233965.39999999991</v>
       </c>
-      <c r="Z5" s="50">
+      <c r="Z5" s="33">
         <v>10000</v>
       </c>
-      <c r="AA5" s="50">
+      <c r="AA5" s="33">
         <v>5000</v>
       </c>
-      <c r="AB5" s="50">
+      <c r="AB5" s="33">
         <v>10000</v>
       </c>
-      <c r="AC5" s="52">
+      <c r="AC5" s="35">
         <f>Y5-Z5-AA5-AB5</f>
         <v>-258965.39999999991</v>
       </c>
@@ -2910,11 +2907,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="30.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="39" t="s">
+    <row r="34" spans="1:10" ht="30.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="B34" s="40"/>
+      <c r="B34" s="54"/>
       <c r="C34" s="18">
         <f>SUM(C3:C33)</f>
         <v>2685553</v>
@@ -2950,6 +2947,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:J1"/>
     <mergeCell ref="Z2:AB2"/>
     <mergeCell ref="Q1:AB1"/>
     <mergeCell ref="T2:U2"/>
@@ -2957,12 +2960,6 @@
     <mergeCell ref="S2:S3"/>
     <mergeCell ref="R2:R3"/>
     <mergeCell ref="Q2:Q3"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="A34:B34"/>
   </mergeCells>
   <conditionalFormatting sqref="I3:J22">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
@@ -2976,84 +2973,84 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A88C44DB-A587-491D-9457-596244BE46D1}">
   <dimension ref="A1:AC34"/>
-  <sheetFormatPr defaultColWidth="9.09765625" defaultRowHeight="30.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="30.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.75" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.09765625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="11.796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="13.09765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.09765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="8.09765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="9.09765625" style="1"/>
-    <col min="13" max="13" width="55.796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.09765625" style="1"/>
+    <col min="3" max="3" width="13.125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="13.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="8.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="9.125" style="1"/>
+    <col min="13" max="13" width="55.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.125" style="1"/>
     <col min="15" max="15" width="43" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9.09765625" style="1"/>
-    <col min="17" max="18" width="15.796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.09765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.125" style="1"/>
+    <col min="17" max="18" width="15.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.125" style="1" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="11.796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.75" style="1" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.09765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="21.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="16.19921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="13.796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="8.796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="24.296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.09765625" style="1"/>
+    <col min="24" max="24" width="13.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="21.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="16.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="8.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="24.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="41" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="43" t="s">
+      <c r="A1" s="47" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43" t="s">
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="43"/>
-      <c r="H1" s="43"/>
-      <c r="I1" s="37" t="s">
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="J1" s="38"/>
-      <c r="M1" s="45" t="s">
+      <c r="J1" s="52"/>
+      <c r="M1" s="31" t="s">
         <v>15</v>
       </c>
       <c r="N1" s="26"/>
-      <c r="O1" s="45" t="s">
+      <c r="O1" s="31" t="s">
         <v>28</v>
       </c>
       <c r="P1" s="26"/>
-      <c r="Q1" s="48" t="s">
+      <c r="Q1" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="R1" s="48"/>
-      <c r="S1" s="48"/>
-      <c r="T1" s="48"/>
-      <c r="U1" s="48"/>
-      <c r="V1" s="48"/>
-      <c r="W1" s="48"/>
-      <c r="X1" s="48"/>
-      <c r="Y1" s="48"/>
-      <c r="Z1" s="48"/>
-      <c r="AA1" s="48"/>
-      <c r="AB1" s="48"/>
-      <c r="AC1" s="48"/>
+      <c r="R1" s="45"/>
+      <c r="S1" s="45"/>
+      <c r="T1" s="45"/>
+      <c r="U1" s="45"/>
+      <c r="V1" s="45"/>
+      <c r="W1" s="45"/>
+      <c r="X1" s="45"/>
+      <c r="Y1" s="45"/>
+      <c r="Z1" s="45"/>
+      <c r="AA1" s="45"/>
+      <c r="AB1" s="45"/>
+      <c r="AC1" s="45"/>
     </row>
     <row r="2" spans="1:29" ht="30.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="42"/>
-      <c r="B2" s="44"/>
+      <c r="A2" s="48"/>
+      <c r="B2" s="50"/>
       <c r="C2" s="8" t="s">
         <v>4</v>
       </c>
@@ -3084,33 +3081,33 @@
       <c r="O2" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="Q2" s="49" t="s">
+      <c r="Q2" s="44" t="s">
         <v>39</v>
       </c>
-      <c r="R2" s="49" t="s">
+      <c r="R2" s="44" t="s">
         <v>49</v>
       </c>
-      <c r="S2" s="49" t="s">
+      <c r="S2" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="T2" s="53" t="s">
+      <c r="T2" s="46" t="s">
         <v>40</v>
       </c>
-      <c r="U2" s="53"/>
-      <c r="V2" s="49" t="s">
+      <c r="U2" s="46"/>
+      <c r="V2" s="44" t="s">
         <v>42</v>
       </c>
-      <c r="W2" s="49"/>
-      <c r="X2" s="49"/>
-      <c r="Y2" s="54" t="s">
+      <c r="W2" s="44"/>
+      <c r="X2" s="44"/>
+      <c r="Y2" s="37" t="s">
         <v>46</v>
       </c>
-      <c r="Z2" s="49" t="s">
+      <c r="Z2" s="44" t="s">
         <v>51</v>
       </c>
-      <c r="AA2" s="49"/>
-      <c r="AB2" s="49"/>
-      <c r="AC2" s="54" t="s">
+      <c r="AA2" s="44"/>
+      <c r="AB2" s="44"/>
+      <c r="AC2" s="37" t="s">
         <v>55</v>
       </c>
     </row>
@@ -3155,13 +3152,13 @@
       <c r="O3" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="Q3" s="49"/>
-      <c r="R3" s="49"/>
-      <c r="S3" s="49"/>
-      <c r="T3" s="55" t="s">
+      <c r="Q3" s="44"/>
+      <c r="R3" s="44"/>
+      <c r="S3" s="44"/>
+      <c r="T3" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="U3" s="55" t="s">
+      <c r="U3" s="36" t="s">
         <v>41</v>
       </c>
       <c r="V3" s="8" t="s">
@@ -3173,7 +3170,7 @@
       <c r="X3" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="Y3" s="54" t="s">
+      <c r="Y3" s="37" t="s">
         <v>47</v>
       </c>
       <c r="Z3" s="8" t="s">
@@ -3185,11 +3182,11 @@
       <c r="AB3" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="AC3" s="54" t="s">
+      <c r="AC3" s="37" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="30.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:29" ht="30.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="11">
         <v>45779</v>
       </c>
@@ -3230,51 +3227,51 @@
       <c r="O4" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="Q4" s="47" t="s">
+      <c r="Q4" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="R4" s="50">
+      <c r="R4" s="33">
         <f>F34</f>
         <v>14338205</v>
       </c>
-      <c r="S4" s="50">
+      <c r="S4" s="33">
         <f>R4*0.86</f>
         <v>12330856.299999999</v>
       </c>
-      <c r="T4" s="51">
+      <c r="T4" s="34">
         <v>192550</v>
       </c>
-      <c r="U4" s="51">
+      <c r="U4" s="34">
         <v>1100000</v>
       </c>
-      <c r="V4" s="50">
+      <c r="V4" s="33">
         <v>70000</v>
       </c>
-      <c r="W4" s="50">
+      <c r="W4" s="33">
         <v>2000</v>
       </c>
-      <c r="X4" s="50">
+      <c r="X4" s="33">
         <v>30000</v>
       </c>
-      <c r="Y4" s="52">
+      <c r="Y4" s="35">
         <f>R4-S4-T4-U4-V4-W4-X4</f>
         <v>612798.70000000112</v>
       </c>
-      <c r="Z4" s="50">
+      <c r="Z4" s="33">
         <v>20000</v>
       </c>
-      <c r="AA4" s="50">
+      <c r="AA4" s="33">
         <v>10000</v>
       </c>
-      <c r="AB4" s="50">
+      <c r="AB4" s="33">
         <v>10000</v>
       </c>
-      <c r="AC4" s="52">
+      <c r="AC4" s="35">
         <f>Y4-Z4-AA4-AB4</f>
         <v>572798.70000000112</v>
       </c>
     </row>
-    <row r="5" spans="1:29" ht="30.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:29" ht="30.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="11">
         <v>45780</v>
       </c>
@@ -3315,46 +3312,46 @@
       <c r="O5" s="29" t="s">
         <v>32</v>
       </c>
-      <c r="Q5" s="47" t="s">
+      <c r="Q5" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="R5" s="50">
+      <c r="R5" s="33">
         <f>G34</f>
         <v>3613638</v>
       </c>
-      <c r="S5" s="50">
+      <c r="S5" s="33">
         <f>R5*0.86</f>
         <v>3107728.68</v>
       </c>
-      <c r="T5" s="51">
+      <c r="T5" s="34">
         <v>60330</v>
       </c>
-      <c r="U5" s="51">
+      <c r="U5" s="34">
         <v>350000</v>
       </c>
-      <c r="V5" s="50">
+      <c r="V5" s="33">
         <v>10000</v>
       </c>
-      <c r="W5" s="50">
+      <c r="W5" s="33">
         <v>2000</v>
       </c>
-      <c r="X5" s="50">
+      <c r="X5" s="33">
         <v>10000</v>
       </c>
-      <c r="Y5" s="52">
+      <c r="Y5" s="35">
         <f>R5-S5-T5-U5-V5-W5-X5</f>
         <v>73579.319999999832</v>
       </c>
-      <c r="Z5" s="50">
+      <c r="Z5" s="33">
         <v>10000</v>
       </c>
-      <c r="AA5" s="50">
+      <c r="AA5" s="33">
         <v>5000</v>
       </c>
-      <c r="AB5" s="50">
+      <c r="AB5" s="33">
         <v>10000</v>
       </c>
-      <c r="AC5" s="52">
+      <c r="AC5" s="35">
         <f>Y5-Z5-AA5-AB5</f>
         <v>48579.319999999832</v>
       </c>
@@ -4391,11 +4388,11 @@
         <v>1.16368</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="30.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="39" t="s">
+    <row r="34" spans="1:10" ht="30.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="B34" s="40"/>
+      <c r="B34" s="54"/>
       <c r="C34" s="18">
         <f>SUM(C3:C33)</f>
         <v>12870000</v>
@@ -4431,11 +4428,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="Q2:Q3"/>
-    <mergeCell ref="R2:R3"/>
-    <mergeCell ref="S2:S3"/>
-    <mergeCell ref="T2:U2"/>
-    <mergeCell ref="V2:X2"/>
     <mergeCell ref="Z2:AB2"/>
     <mergeCell ref="Q1:AC1"/>
     <mergeCell ref="I1:J1"/>
@@ -4444,6 +4436,11 @@
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="F1:H1"/>
+    <mergeCell ref="Q2:Q3"/>
+    <mergeCell ref="R2:R3"/>
+    <mergeCell ref="S2:S3"/>
+    <mergeCell ref="T2:U2"/>
+    <mergeCell ref="V2:X2"/>
   </mergeCells>
   <conditionalFormatting sqref="I3:J22">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
@@ -4458,83 +4455,81 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5332805-568C-411E-8C5D-32B663A517E8}">
   <dimension ref="A1:AC34"/>
-  <sheetFormatPr defaultColWidth="9.09765625" defaultRowHeight="30.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="30.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.8984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.09765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.09765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.3984375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.59765625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="8.09765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9" style="1" customWidth="1"/>
-    <col min="11" max="12" width="9.09765625" style="1"/>
-    <col min="13" max="13" width="53.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="9.09765625" style="1"/>
-    <col min="17" max="17" width="15.09765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="15.19921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="12.19921875" style="1" customWidth="1"/>
-    <col min="20" max="20" width="12.296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.19921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="12.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="20.8984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="15.69921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="13.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="8.19921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="23.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.09765625" style="1"/>
+    <col min="1" max="1" width="11.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="11.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.625" style="1" customWidth="1"/>
+    <col min="9" max="10" width="8.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="9.125" style="1"/>
+    <col min="13" max="13" width="54.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="9.125" style="1"/>
+    <col min="17" max="17" width="15.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="21.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="16.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="8.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="23.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="41" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="43" t="s">
+      <c r="A1" s="47" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43" t="s">
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="43"/>
-      <c r="H1" s="43"/>
-      <c r="I1" s="37" t="s">
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="J1" s="38"/>
+      <c r="J1" s="52"/>
       <c r="M1" s="27" t="s">
         <v>15</v>
       </c>
       <c r="N1" s="26"/>
       <c r="O1" s="26"/>
       <c r="P1" s="26"/>
-      <c r="Q1" s="48" t="s">
+      <c r="Q1" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="R1" s="48"/>
-      <c r="S1" s="48"/>
-      <c r="T1" s="48"/>
-      <c r="U1" s="48"/>
-      <c r="V1" s="48"/>
-      <c r="W1" s="48"/>
-      <c r="X1" s="48"/>
-      <c r="Y1" s="48"/>
-      <c r="Z1" s="48"/>
-      <c r="AA1" s="48"/>
-      <c r="AB1" s="48"/>
-      <c r="AC1" s="48"/>
+      <c r="R1" s="45"/>
+      <c r="S1" s="45"/>
+      <c r="T1" s="45"/>
+      <c r="U1" s="45"/>
+      <c r="V1" s="45"/>
+      <c r="W1" s="45"/>
+      <c r="X1" s="45"/>
+      <c r="Y1" s="45"/>
+      <c r="Z1" s="45"/>
+      <c r="AA1" s="45"/>
+      <c r="AB1" s="45"/>
+      <c r="AC1" s="45"/>
     </row>
     <row r="2" spans="1:29" ht="30.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="42"/>
-      <c r="B2" s="44"/>
+      <c r="A2" s="48"/>
+      <c r="B2" s="50"/>
       <c r="C2" s="8" t="s">
         <v>4</v>
       </c>
@@ -4562,33 +4557,33 @@
       <c r="M2" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="Q2" s="49" t="s">
+      <c r="Q2" s="44" t="s">
         <v>39</v>
       </c>
-      <c r="R2" s="49" t="s">
+      <c r="R2" s="44" t="s">
         <v>49</v>
       </c>
-      <c r="S2" s="49" t="s">
+      <c r="S2" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="T2" s="53" t="s">
+      <c r="T2" s="46" t="s">
         <v>40</v>
       </c>
-      <c r="U2" s="53"/>
-      <c r="V2" s="49" t="s">
+      <c r="U2" s="46"/>
+      <c r="V2" s="44" t="s">
         <v>42</v>
       </c>
-      <c r="W2" s="49"/>
-      <c r="X2" s="49"/>
-      <c r="Y2" s="54" t="s">
+      <c r="W2" s="44"/>
+      <c r="X2" s="44"/>
+      <c r="Y2" s="37" t="s">
         <v>46</v>
       </c>
-      <c r="Z2" s="49" t="s">
+      <c r="Z2" s="44" t="s">
         <v>51</v>
       </c>
-      <c r="AA2" s="49"/>
-      <c r="AB2" s="49"/>
-      <c r="AC2" s="54" t="s">
+      <c r="AA2" s="44"/>
+      <c r="AB2" s="44"/>
+      <c r="AC2" s="37" t="s">
         <v>55</v>
       </c>
     </row>
@@ -4630,13 +4625,13 @@
       <c r="M3" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="Q3" s="49"/>
-      <c r="R3" s="49"/>
-      <c r="S3" s="49"/>
-      <c r="T3" s="55" t="s">
+      <c r="Q3" s="44"/>
+      <c r="R3" s="44"/>
+      <c r="S3" s="44"/>
+      <c r="T3" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="U3" s="55" t="s">
+      <c r="U3" s="36" t="s">
         <v>41</v>
       </c>
       <c r="V3" s="8" t="s">
@@ -4648,7 +4643,7 @@
       <c r="X3" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="Y3" s="54" t="s">
+      <c r="Y3" s="37" t="s">
         <v>47</v>
       </c>
       <c r="Z3" s="8" t="s">
@@ -4660,11 +4655,11 @@
       <c r="AB3" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="AC3" s="54" t="s">
+      <c r="AC3" s="37" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="30.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:29" ht="30.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="11">
         <v>45810</v>
       </c>
@@ -4678,7 +4673,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="14">
-        <f t="shared" ref="E4:E33" si="0">D4+C4</f>
+        <f t="shared" ref="E4:E32" si="0">D4+C4</f>
         <v>350000</v>
       </c>
       <c r="F4" s="13">
@@ -4696,57 +4691,57 @@
         <v>1.2182314285714286</v>
       </c>
       <c r="J4" s="25">
-        <f t="shared" ref="J4:J33" si="2">IF(G4&lt;&gt;0,G4/D4,1)</f>
+        <f t="shared" ref="I4:J33" si="2">IF(G4&lt;&gt;0,G4/D4,1)</f>
         <v>1</v>
       </c>
       <c r="M4" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="Q4" s="47" t="s">
+      <c r="Q4" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="R4" s="50">
+      <c r="R4" s="33">
         <f>F34</f>
-        <v>3118295</v>
-      </c>
-      <c r="S4" s="50">
+        <v>9089291</v>
+      </c>
+      <c r="S4" s="33">
         <f>R4*0.86</f>
-        <v>2681733.7000000002</v>
-      </c>
-      <c r="T4" s="51">
+        <v>7816790.2599999998</v>
+      </c>
+      <c r="T4" s="34">
         <v>192550</v>
       </c>
-      <c r="U4" s="51">
+      <c r="U4" s="34">
         <v>1100000</v>
       </c>
-      <c r="V4" s="50">
+      <c r="V4" s="33">
         <v>80000</v>
       </c>
-      <c r="W4" s="50">
+      <c r="W4" s="33">
         <v>2000</v>
       </c>
-      <c r="X4" s="50">
+      <c r="X4" s="33">
         <v>30000</v>
       </c>
-      <c r="Y4" s="52">
+      <c r="Y4" s="35">
         <f>R4-S4-T4-U4-V4-W4-X4</f>
-        <v>-967988.70000000019</v>
-      </c>
-      <c r="Z4" s="50">
+        <v>-132049.25999999978</v>
+      </c>
+      <c r="Z4" s="33">
         <v>20000</v>
       </c>
-      <c r="AA4" s="50">
+      <c r="AA4" s="33">
         <v>10000</v>
       </c>
-      <c r="AB4" s="50">
+      <c r="AB4" s="33">
         <v>10000</v>
       </c>
-      <c r="AC4" s="52">
+      <c r="AC4" s="35">
         <f>Y4-Z4-AA4-AB4</f>
-        <v>-1007988.7000000002</v>
-      </c>
-    </row>
-    <row r="5" spans="1:29" ht="30.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+        <v>-172049.25999999978</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29" ht="30.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="11">
         <v>45811</v>
       </c>
@@ -4784,48 +4779,48 @@
       <c r="M5" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="Q5" s="47" t="s">
+      <c r="Q5" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="R5" s="50">
+      <c r="R5" s="33">
         <f>G34</f>
-        <v>800775</v>
-      </c>
-      <c r="S5" s="50">
+        <v>2373297</v>
+      </c>
+      <c r="S5" s="33">
         <f>R5*0.86</f>
-        <v>688666.5</v>
-      </c>
-      <c r="T5" s="51">
+        <v>2041035.42</v>
+      </c>
+      <c r="T5" s="34">
         <v>60330</v>
       </c>
-      <c r="U5" s="51">
+      <c r="U5" s="34">
         <v>350000</v>
       </c>
-      <c r="V5" s="50">
+      <c r="V5" s="33">
         <v>10000</v>
       </c>
-      <c r="W5" s="50">
+      <c r="W5" s="33">
         <v>2000</v>
       </c>
-      <c r="X5" s="50">
+      <c r="X5" s="33">
         <v>10000</v>
       </c>
-      <c r="Y5" s="52">
+      <c r="Y5" s="35">
         <f>R5-S5-T5-U5-V5-W5-X5</f>
-        <v>-320221.5</v>
-      </c>
-      <c r="Z5" s="50">
+        <v>-100068.41999999993</v>
+      </c>
+      <c r="Z5" s="33">
         <v>10000</v>
       </c>
-      <c r="AA5" s="50">
+      <c r="AA5" s="33">
         <v>5000</v>
       </c>
-      <c r="AB5" s="50">
+      <c r="AB5" s="33">
         <v>10000</v>
       </c>
-      <c r="AC5" s="52">
+      <c r="AC5" s="35">
         <f>Y5-Z5-AA5-AB5</f>
-        <v>-345221.5</v>
+        <v>-125068.41999999993</v>
       </c>
     </row>
     <row r="6" spans="1:29" ht="30.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -5037,15 +5032,19 @@
         <f t="shared" si="0"/>
         <v>400000</v>
       </c>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
+      <c r="F11" s="13">
+        <v>311275</v>
+      </c>
+      <c r="G11" s="13">
+        <v>0</v>
+      </c>
       <c r="H11" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>311275</v>
       </c>
       <c r="I11" s="24">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.77818750000000003</v>
       </c>
       <c r="J11" s="25">
         <f t="shared" si="2"/>
@@ -5072,19 +5071,23 @@
         <f t="shared" si="0"/>
         <v>400000</v>
       </c>
-      <c r="F12" s="13"/>
-      <c r="G12" s="13"/>
+      <c r="F12" s="13">
+        <v>236254</v>
+      </c>
+      <c r="G12" s="13">
+        <v>176447</v>
+      </c>
       <c r="H12" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>412701</v>
       </c>
       <c r="I12" s="24">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.94501599999999997</v>
       </c>
       <c r="J12" s="25">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>1.1763133333333333</v>
       </c>
       <c r="M12" s="29" t="s">
         <v>26</v>
@@ -5107,19 +5110,23 @@
         <f t="shared" si="0"/>
         <v>500000</v>
       </c>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
+      <c r="F13" s="13">
+        <v>466776</v>
+      </c>
+      <c r="G13" s="13">
+        <v>143292</v>
+      </c>
       <c r="H13" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>610068</v>
       </c>
       <c r="I13" s="24">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1.3336457142857143</v>
       </c>
       <c r="J13" s="25">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0.95528000000000002</v>
       </c>
       <c r="M13" s="29" t="s">
         <v>27</v>
@@ -5142,19 +5149,23 @@
         <f t="shared" si="0"/>
         <v>700000</v>
       </c>
-      <c r="F14" s="13"/>
-      <c r="G14" s="13"/>
+      <c r="F14" s="13">
+        <v>705724</v>
+      </c>
+      <c r="G14" s="13">
+        <v>140050</v>
+      </c>
       <c r="H14" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>845774</v>
       </c>
       <c r="I14" s="24">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1.1762066666666666</v>
       </c>
       <c r="J14" s="25">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>1.4005000000000001</v>
       </c>
       <c r="M14" s="29"/>
     </row>
@@ -5175,19 +5186,23 @@
         <f t="shared" si="0"/>
         <v>900000</v>
       </c>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
+      <c r="F15" s="13">
+        <v>960339</v>
+      </c>
+      <c r="G15" s="13">
+        <v>193947</v>
+      </c>
       <c r="H15" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1154286</v>
       </c>
       <c r="I15" s="24">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1.3719128571428572</v>
       </c>
       <c r="J15" s="25">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0.96973500000000001</v>
       </c>
       <c r="M15" s="29"/>
     </row>
@@ -5208,19 +5223,23 @@
         <f t="shared" si="0"/>
         <v>550000</v>
       </c>
-      <c r="F16" s="13"/>
-      <c r="G16" s="13"/>
+      <c r="F16" s="13">
+        <v>499306</v>
+      </c>
+      <c r="G16" s="13">
+        <v>159370</v>
+      </c>
       <c r="H16" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>658676</v>
       </c>
       <c r="I16" s="24">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1.248265</v>
       </c>
       <c r="J16" s="25">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>1.0624666666666667</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="30.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -5240,19 +5259,23 @@
         <f t="shared" si="0"/>
         <v>350000</v>
       </c>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
+      <c r="F17" s="13">
+        <v>238816</v>
+      </c>
+      <c r="G17" s="13">
+        <v>55915</v>
+      </c>
       <c r="H17" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>294731</v>
       </c>
       <c r="I17" s="24">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.955264</v>
       </c>
       <c r="J17" s="25">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0.55915000000000004</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="30.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -5272,15 +5295,19 @@
         <f t="shared" si="0"/>
         <v>350000</v>
       </c>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
+      <c r="F18" s="13">
+        <v>450128</v>
+      </c>
+      <c r="G18" s="13">
+        <v>0</v>
+      </c>
       <c r="H18" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>450128</v>
       </c>
       <c r="I18" s="24">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1.2860799999999999</v>
       </c>
       <c r="J18" s="25">
         <f t="shared" si="2"/>
@@ -5304,19 +5331,23 @@
         <f t="shared" si="0"/>
         <v>320000</v>
       </c>
-      <c r="F19" s="13"/>
-      <c r="G19" s="13"/>
+      <c r="F19" s="13">
+        <v>230669</v>
+      </c>
+      <c r="G19" s="13">
+        <v>150634</v>
+      </c>
       <c r="H19" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>381303</v>
       </c>
       <c r="I19" s="24">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1.1533450000000001</v>
       </c>
       <c r="J19" s="25">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>1.2552833333333333</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="30.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -5336,19 +5367,23 @@
         <f t="shared" si="0"/>
         <v>500000</v>
       </c>
-      <c r="F20" s="13"/>
-      <c r="G20" s="13"/>
+      <c r="F20" s="13">
+        <v>368131</v>
+      </c>
+      <c r="G20" s="13">
+        <v>40765</v>
+      </c>
       <c r="H20" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>408896</v>
       </c>
       <c r="I20" s="24">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.92032749999999997</v>
       </c>
       <c r="J20" s="25">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0.40765000000000001</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="30.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -5368,19 +5403,23 @@
         <f t="shared" si="0"/>
         <v>700000</v>
       </c>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
+      <c r="F21" s="13">
+        <v>371746</v>
+      </c>
+      <c r="G21" s="13">
+        <v>72079</v>
+      </c>
       <c r="H21" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>443825</v>
       </c>
       <c r="I21" s="24">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.61957666666666666</v>
       </c>
       <c r="J21" s="25">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0.72079000000000004</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="30.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -5400,19 +5439,23 @@
         <f t="shared" si="0"/>
         <v>830000</v>
       </c>
-      <c r="F22" s="13"/>
-      <c r="G22" s="13"/>
+      <c r="F22" s="13">
+        <v>725032</v>
+      </c>
+      <c r="G22" s="13">
+        <v>254753</v>
+      </c>
       <c r="H22" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>979785</v>
       </c>
       <c r="I22" s="24">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1.1154338461538462</v>
       </c>
       <c r="J22" s="25">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>1.4152944444444444</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="30.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -5432,19 +5475,23 @@
         <f t="shared" si="0"/>
         <v>470000</v>
       </c>
-      <c r="F23" s="13"/>
-      <c r="G23" s="13"/>
+      <c r="F23" s="13">
+        <v>406800</v>
+      </c>
+      <c r="G23" s="13">
+        <v>185270</v>
+      </c>
       <c r="H23" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>592070</v>
       </c>
       <c r="I23" s="24">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1.1622857142857144</v>
       </c>
       <c r="J23" s="25">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>1.5439166666666666</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="30.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -5470,9 +5517,9 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I24" s="24">
-        <f t="shared" si="3"/>
-        <v>0</v>
+      <c r="I24" s="25">
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="J24" s="25">
         <f t="shared" si="2"/>
@@ -5502,9 +5549,9 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I25" s="24">
-        <f t="shared" si="3"/>
-        <v>0</v>
+      <c r="I25" s="25">
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="J25" s="25">
         <f t="shared" si="2"/>
@@ -5534,9 +5581,9 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I26" s="24">
-        <f t="shared" si="3"/>
-        <v>0</v>
+      <c r="I26" s="25">
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="J26" s="25">
         <f t="shared" si="2"/>
@@ -5566,9 +5613,9 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I27" s="24">
-        <f t="shared" si="3"/>
-        <v>0</v>
+      <c r="I27" s="25">
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="J27" s="25">
         <f t="shared" si="2"/>
@@ -5598,9 +5645,9 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I28" s="24">
-        <f t="shared" si="3"/>
-        <v>0</v>
+      <c r="I28" s="25">
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="J28" s="25">
         <f t="shared" si="2"/>
@@ -5630,9 +5677,9 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I29" s="24">
-        <f t="shared" si="3"/>
-        <v>0</v>
+      <c r="I29" s="25">
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="J29" s="25">
         <f t="shared" si="2"/>
@@ -5662,9 +5709,9 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I30" s="24">
-        <f t="shared" si="3"/>
-        <v>0</v>
+      <c r="I30" s="25">
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="J30" s="25">
         <f t="shared" si="2"/>
@@ -5694,9 +5741,9 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I31" s="24">
-        <f t="shared" si="3"/>
-        <v>0</v>
+      <c r="I31" s="25">
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="J31" s="25">
         <f t="shared" si="2"/>
@@ -5726,9 +5773,9 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I32" s="24">
-        <f t="shared" si="3"/>
-        <v>0</v>
+      <c r="I32" s="25">
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="J32" s="25">
         <f t="shared" si="2"/>
@@ -5753,11 +5800,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="30.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="39" t="s">
+    <row r="34" spans="1:10" ht="30.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="B34" s="40"/>
+      <c r="B34" s="54"/>
       <c r="C34" s="18">
         <f>SUM(C3:C33)</f>
         <v>12000000</v>
@@ -5772,27 +5819,33 @@
       </c>
       <c r="F34" s="18">
         <f t="shared" ref="F34:H34" si="4">SUM(F3:F33)</f>
-        <v>3118295</v>
+        <v>9089291</v>
       </c>
       <c r="G34" s="18">
         <f t="shared" si="4"/>
-        <v>800775</v>
+        <v>2373297</v>
       </c>
       <c r="H34" s="18">
         <f t="shared" si="4"/>
-        <v>3919070</v>
-      </c>
-      <c r="I34" s="46">
-        <f>F34/C34</f>
-        <v>0.25985791666666669</v>
+        <v>11462588</v>
+      </c>
+      <c r="I34" s="20">
+        <f>AVERAGE(I3:I33)</f>
+        <v>1.0380158131257631</v>
       </c>
       <c r="J34" s="20">
         <f>AVERAGE(J3:J33)</f>
-        <v>0.96378784946236562</v>
+        <v>0.97883234767025107</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:J1"/>
     <mergeCell ref="Q1:AC1"/>
     <mergeCell ref="Q2:Q3"/>
     <mergeCell ref="R2:R3"/>
@@ -5800,12 +5853,6 @@
     <mergeCell ref="T2:U2"/>
     <mergeCell ref="V2:X2"/>
     <mergeCell ref="Z2:AB2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="A34:B34"/>
   </mergeCells>
   <conditionalFormatting sqref="I3:J22">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">

--- a/Tạp hóa/Kế hoạch kinh doanh/Kế hoạch kinh doanh.xlsx
+++ b/Tạp hóa/Kế hoạch kinh doanh/Kế hoạch kinh doanh.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LeVeL infinity\Desktop\BackUp\backup-PC\Tạp hóa\Kế hoạch kinh doanh\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EA8AE97-5B76-415C-B56B-F1701F9C1D61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{070E46E8-D61E-48E7-B773-C9097A5D6CE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="3" xr2:uid="{AC7C96C8-729D-4A1A-A481-EBFA6B52E612}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{AC7C96C8-729D-4A1A-A481-EBFA6B52E612}"/>
   </bookViews>
   <sheets>
     <sheet name="Mẫu" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="58">
   <si>
     <t>日付</t>
   </si>
@@ -200,6 +200,9 @@
   <si>
     <t>(= Y-Z-AA-AB)</t>
   </si>
+  <si>
+    <t>TĂNG THÊM 1 SỐ MÃ HÀNG NƯỚC NGOÀI</t>
+  </si>
 </sst>
 </file>
 
@@ -291,7 +294,7 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -364,6 +367,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="21">
     <border>
@@ -656,7 +665,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -759,6 +768,9 @@
     <xf numFmtId="0" fontId="11" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -777,6 +789,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -785,6 +803,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -797,18 +821,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1171,30 +1183,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="42" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="41" t="s">
+      <c r="A1" s="43" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="38" t="s">
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="39"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="38" t="s">
+      <c r="G1" s="40"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="J1" s="39"/>
+      <c r="J1" s="40"/>
     </row>
     <row r="2" spans="1:10" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="43"/>
-      <c r="B2" s="43"/>
+      <c r="A2" s="44"/>
+      <c r="B2" s="44"/>
       <c r="C2" s="2" t="s">
         <v>4</v>
       </c>
@@ -1735,26 +1747,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="49" t="s">
+      <c r="A1" s="52" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="54" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49" t="s">
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="51" t="s">
+      <c r="G1" s="54"/>
+      <c r="H1" s="54"/>
+      <c r="I1" s="45" t="s">
         <v>14</v>
       </c>
-      <c r="J1" s="52"/>
+      <c r="J1" s="46"/>
       <c r="M1" s="31" t="s">
         <v>15</v>
       </c>
@@ -1763,24 +1775,24 @@
         <v>28</v>
       </c>
       <c r="P1" s="26"/>
-      <c r="Q1" s="45" t="s">
+      <c r="Q1" s="48" t="s">
         <v>36</v>
       </c>
-      <c r="R1" s="45"/>
-      <c r="S1" s="45"/>
-      <c r="T1" s="45"/>
-      <c r="U1" s="45"/>
-      <c r="V1" s="45"/>
-      <c r="W1" s="45"/>
-      <c r="X1" s="45"/>
-      <c r="Y1" s="45"/>
-      <c r="Z1" s="45"/>
-      <c r="AA1" s="45"/>
-      <c r="AB1" s="45"/>
+      <c r="R1" s="48"/>
+      <c r="S1" s="48"/>
+      <c r="T1" s="48"/>
+      <c r="U1" s="48"/>
+      <c r="V1" s="48"/>
+      <c r="W1" s="48"/>
+      <c r="X1" s="48"/>
+      <c r="Y1" s="48"/>
+      <c r="Z1" s="48"/>
+      <c r="AA1" s="48"/>
+      <c r="AB1" s="48"/>
     </row>
     <row r="2" spans="1:29" ht="30.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="48"/>
-      <c r="B2" s="50"/>
+      <c r="A2" s="53"/>
+      <c r="B2" s="55"/>
       <c r="C2" s="8" t="s">
         <v>4</v>
       </c>
@@ -1811,32 +1823,32 @@
       <c r="O2" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="Q2" s="44" t="s">
+      <c r="Q2" s="47" t="s">
         <v>39</v>
       </c>
-      <c r="R2" s="44" t="s">
+      <c r="R2" s="47" t="s">
         <v>49</v>
       </c>
-      <c r="S2" s="44" t="s">
+      <c r="S2" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="T2" s="46" t="s">
+      <c r="T2" s="49" t="s">
         <v>40</v>
       </c>
-      <c r="U2" s="46"/>
-      <c r="V2" s="44" t="s">
+      <c r="U2" s="49"/>
+      <c r="V2" s="47" t="s">
         <v>42</v>
       </c>
-      <c r="W2" s="44"/>
-      <c r="X2" s="44"/>
+      <c r="W2" s="47"/>
+      <c r="X2" s="47"/>
       <c r="Y2" s="37" t="s">
         <v>46</v>
       </c>
-      <c r="Z2" s="44" t="s">
+      <c r="Z2" s="47" t="s">
         <v>51</v>
       </c>
-      <c r="AA2" s="44"/>
-      <c r="AB2" s="44"/>
+      <c r="AA2" s="47"/>
+      <c r="AB2" s="47"/>
       <c r="AC2" s="37" t="s">
         <v>55</v>
       </c>
@@ -1874,9 +1886,9 @@
       <c r="O3" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="Q3" s="44"/>
-      <c r="R3" s="44"/>
-      <c r="S3" s="44"/>
+      <c r="Q3" s="47"/>
+      <c r="R3" s="47"/>
+      <c r="S3" s="47"/>
       <c r="T3" s="36" t="s">
         <v>48</v>
       </c>
@@ -2908,10 +2920,10 @@
       </c>
     </row>
     <row r="34" spans="1:10" ht="30.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="53" t="s">
+      <c r="A34" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="B34" s="54"/>
+      <c r="B34" s="51"/>
       <c r="C34" s="18">
         <f>SUM(C3:C33)</f>
         <v>2685553</v>
@@ -3004,26 +3016,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="49" t="s">
+      <c r="A1" s="52" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="54" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49" t="s">
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="51" t="s">
+      <c r="G1" s="54"/>
+      <c r="H1" s="54"/>
+      <c r="I1" s="45" t="s">
         <v>14</v>
       </c>
-      <c r="J1" s="52"/>
+      <c r="J1" s="46"/>
       <c r="M1" s="31" t="s">
         <v>15</v>
       </c>
@@ -3032,25 +3044,25 @@
         <v>28</v>
       </c>
       <c r="P1" s="26"/>
-      <c r="Q1" s="45" t="s">
+      <c r="Q1" s="48" t="s">
         <v>36</v>
       </c>
-      <c r="R1" s="45"/>
-      <c r="S1" s="45"/>
-      <c r="T1" s="45"/>
-      <c r="U1" s="45"/>
-      <c r="V1" s="45"/>
-      <c r="W1" s="45"/>
-      <c r="X1" s="45"/>
-      <c r="Y1" s="45"/>
-      <c r="Z1" s="45"/>
-      <c r="AA1" s="45"/>
-      <c r="AB1" s="45"/>
-      <c r="AC1" s="45"/>
+      <c r="R1" s="48"/>
+      <c r="S1" s="48"/>
+      <c r="T1" s="48"/>
+      <c r="U1" s="48"/>
+      <c r="V1" s="48"/>
+      <c r="W1" s="48"/>
+      <c r="X1" s="48"/>
+      <c r="Y1" s="48"/>
+      <c r="Z1" s="48"/>
+      <c r="AA1" s="48"/>
+      <c r="AB1" s="48"/>
+      <c r="AC1" s="48"/>
     </row>
     <row r="2" spans="1:29" ht="30.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="48"/>
-      <c r="B2" s="50"/>
+      <c r="A2" s="53"/>
+      <c r="B2" s="55"/>
       <c r="C2" s="8" t="s">
         <v>4</v>
       </c>
@@ -3081,32 +3093,32 @@
       <c r="O2" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="Q2" s="44" t="s">
+      <c r="Q2" s="47" t="s">
         <v>39</v>
       </c>
-      <c r="R2" s="44" t="s">
+      <c r="R2" s="47" t="s">
         <v>49</v>
       </c>
-      <c r="S2" s="44" t="s">
+      <c r="S2" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="T2" s="46" t="s">
+      <c r="T2" s="49" t="s">
         <v>40</v>
       </c>
-      <c r="U2" s="46"/>
-      <c r="V2" s="44" t="s">
+      <c r="U2" s="49"/>
+      <c r="V2" s="47" t="s">
         <v>42</v>
       </c>
-      <c r="W2" s="44"/>
-      <c r="X2" s="44"/>
+      <c r="W2" s="47"/>
+      <c r="X2" s="47"/>
       <c r="Y2" s="37" t="s">
         <v>46</v>
       </c>
-      <c r="Z2" s="44" t="s">
+      <c r="Z2" s="47" t="s">
         <v>51</v>
       </c>
-      <c r="AA2" s="44"/>
-      <c r="AB2" s="44"/>
+      <c r="AA2" s="47"/>
+      <c r="AB2" s="47"/>
       <c r="AC2" s="37" t="s">
         <v>55</v>
       </c>
@@ -3152,9 +3164,9 @@
       <c r="O3" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="Q3" s="44"/>
-      <c r="R3" s="44"/>
-      <c r="S3" s="44"/>
+      <c r="Q3" s="47"/>
+      <c r="R3" s="47"/>
+      <c r="S3" s="47"/>
       <c r="T3" s="36" t="s">
         <v>48</v>
       </c>
@@ -4389,10 +4401,10 @@
       </c>
     </row>
     <row r="34" spans="1:10" ht="30.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="53" t="s">
+      <c r="A34" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="B34" s="54"/>
+      <c r="B34" s="51"/>
       <c r="C34" s="18">
         <f>SUM(C3:C33)</f>
         <v>12870000</v>
@@ -4485,51 +4497,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="49" t="s">
+      <c r="A1" s="52" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="54" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49" t="s">
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="51" t="s">
+      <c r="G1" s="54"/>
+      <c r="H1" s="54"/>
+      <c r="I1" s="45" t="s">
         <v>14</v>
       </c>
-      <c r="J1" s="52"/>
+      <c r="J1" s="46"/>
       <c r="M1" s="27" t="s">
         <v>15</v>
       </c>
       <c r="N1" s="26"/>
       <c r="O1" s="26"/>
       <c r="P1" s="26"/>
-      <c r="Q1" s="45" t="s">
+      <c r="Q1" s="48" t="s">
         <v>36</v>
       </c>
-      <c r="R1" s="45"/>
-      <c r="S1" s="45"/>
-      <c r="T1" s="45"/>
-      <c r="U1" s="45"/>
-      <c r="V1" s="45"/>
-      <c r="W1" s="45"/>
-      <c r="X1" s="45"/>
-      <c r="Y1" s="45"/>
-      <c r="Z1" s="45"/>
-      <c r="AA1" s="45"/>
-      <c r="AB1" s="45"/>
-      <c r="AC1" s="45"/>
+      <c r="R1" s="48"/>
+      <c r="S1" s="48"/>
+      <c r="T1" s="48"/>
+      <c r="U1" s="48"/>
+      <c r="V1" s="48"/>
+      <c r="W1" s="48"/>
+      <c r="X1" s="48"/>
+      <c r="Y1" s="48"/>
+      <c r="Z1" s="48"/>
+      <c r="AA1" s="48"/>
+      <c r="AB1" s="48"/>
+      <c r="AC1" s="48"/>
     </row>
     <row r="2" spans="1:29" ht="30.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="48"/>
-      <c r="B2" s="50"/>
+      <c r="A2" s="53"/>
+      <c r="B2" s="55"/>
       <c r="C2" s="8" t="s">
         <v>4</v>
       </c>
@@ -4557,32 +4569,32 @@
       <c r="M2" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="Q2" s="44" t="s">
+      <c r="Q2" s="47" t="s">
         <v>39</v>
       </c>
-      <c r="R2" s="44" t="s">
+      <c r="R2" s="47" t="s">
         <v>49</v>
       </c>
-      <c r="S2" s="44" t="s">
+      <c r="S2" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="T2" s="46" t="s">
+      <c r="T2" s="49" t="s">
         <v>40</v>
       </c>
-      <c r="U2" s="46"/>
-      <c r="V2" s="44" t="s">
+      <c r="U2" s="49"/>
+      <c r="V2" s="47" t="s">
         <v>42</v>
       </c>
-      <c r="W2" s="44"/>
-      <c r="X2" s="44"/>
+      <c r="W2" s="47"/>
+      <c r="X2" s="47"/>
       <c r="Y2" s="37" t="s">
         <v>46</v>
       </c>
-      <c r="Z2" s="44" t="s">
+      <c r="Z2" s="47" t="s">
         <v>51</v>
       </c>
-      <c r="AA2" s="44"/>
-      <c r="AB2" s="44"/>
+      <c r="AA2" s="47"/>
+      <c r="AB2" s="47"/>
       <c r="AC2" s="37" t="s">
         <v>55</v>
       </c>
@@ -4625,9 +4637,9 @@
       <c r="M3" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="Q3" s="44"/>
-      <c r="R3" s="44"/>
-      <c r="S3" s="44"/>
+      <c r="Q3" s="47"/>
+      <c r="R3" s="47"/>
+      <c r="S3" s="47"/>
       <c r="T3" s="36" t="s">
         <v>48</v>
       </c>
@@ -4702,11 +4714,11 @@
       </c>
       <c r="R4" s="33">
         <f>F34</f>
-        <v>9089291</v>
+        <v>9314611</v>
       </c>
       <c r="S4" s="33">
         <f>R4*0.86</f>
-        <v>7816790.2599999998</v>
+        <v>8010565.46</v>
       </c>
       <c r="T4" s="34">
         <v>192550</v>
@@ -4725,7 +4737,7 @@
       </c>
       <c r="Y4" s="35">
         <f>R4-S4-T4-U4-V4-W4-X4</f>
-        <v>-132049.25999999978</v>
+        <v>-100504.45999999996</v>
       </c>
       <c r="Z4" s="33">
         <v>20000</v>
@@ -4738,7 +4750,7 @@
       </c>
       <c r="AC4" s="35">
         <f>Y4-Z4-AA4-AB4</f>
-        <v>-172049.25999999978</v>
+        <v>-140504.45999999996</v>
       </c>
     </row>
     <row r="5" spans="1:29" ht="30.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -4769,7 +4781,7 @@
         <v>285457</v>
       </c>
       <c r="I5" s="24">
-        <f t="shared" ref="I5:I32" si="3">F5/C5</f>
+        <f t="shared" ref="I5:I23" si="3">F5/C5</f>
         <v>1.052155</v>
       </c>
       <c r="J5" s="25">
@@ -4784,11 +4796,11 @@
       </c>
       <c r="R5" s="33">
         <f>G34</f>
-        <v>2373297</v>
+        <v>2490224</v>
       </c>
       <c r="S5" s="33">
         <f>R5*0.86</f>
-        <v>2041035.42</v>
+        <v>2141592.64</v>
       </c>
       <c r="T5" s="34">
         <v>60330</v>
@@ -4807,7 +4819,7 @@
       </c>
       <c r="Y5" s="35">
         <f>R5-S5-T5-U5-V5-W5-X5</f>
-        <v>-100068.41999999993</v>
+        <v>-83698.64000000013</v>
       </c>
       <c r="Z5" s="33">
         <v>10000</v>
@@ -4820,7 +4832,7 @@
       </c>
       <c r="AC5" s="35">
         <f>Y5-Z5-AA5-AB5</f>
-        <v>-125068.41999999993</v>
+        <v>-108698.64000000013</v>
       </c>
     </row>
     <row r="6" spans="1:29" ht="30.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -5167,7 +5179,9 @@
         <f t="shared" si="2"/>
         <v>1.4005000000000001</v>
       </c>
-      <c r="M14" s="29"/>
+      <c r="M14" s="38" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="15" spans="1:29" ht="30.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="11">
@@ -5511,19 +5525,23 @@
         <f t="shared" si="0"/>
         <v>320000</v>
       </c>
-      <c r="F24" s="13"/>
-      <c r="G24" s="13"/>
+      <c r="F24" s="13">
+        <v>225320</v>
+      </c>
+      <c r="G24" s="13">
+        <v>116927</v>
+      </c>
       <c r="H24" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>342247</v>
       </c>
       <c r="I24" s="25">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>1.1266</v>
       </c>
       <c r="J24" s="25">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0.97439166666666666</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="30.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -5801,10 +5819,10 @@
       </c>
     </row>
     <row r="34" spans="1:10" ht="30.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="53" t="s">
+      <c r="A34" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="B34" s="54"/>
+      <c r="B34" s="51"/>
       <c r="C34" s="18">
         <f>SUM(C3:C33)</f>
         <v>12000000</v>
@@ -5819,23 +5837,23 @@
       </c>
       <c r="F34" s="18">
         <f t="shared" ref="F34:H34" si="4">SUM(F3:F33)</f>
-        <v>9089291</v>
+        <v>9314611</v>
       </c>
       <c r="G34" s="18">
         <f t="shared" si="4"/>
-        <v>2373297</v>
+        <v>2490224</v>
       </c>
       <c r="H34" s="18">
         <f t="shared" si="4"/>
-        <v>11462588</v>
+        <v>11804835</v>
       </c>
       <c r="I34" s="20">
         <f>AVERAGE(I3:I33)</f>
-        <v>1.0380158131257631</v>
+        <v>1.0422358131257632</v>
       </c>
       <c r="J34" s="20">
         <f>AVERAGE(J3:J33)</f>
-        <v>0.97883234767025107</v>
+        <v>0.97800627240143378</v>
       </c>
     </row>
   </sheetData>
